--- a/reports/pdf_weekly_20261002.xlsx
+++ b/reports/pdf_weekly_20261002.xlsx
@@ -560,7 +560,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,035억   ·   현금 36억(0.7%)      주말 2026-10-02  vs  주초 2026-09-28      매수 9종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,330억   ·   현금 18억(0.3%)      주말 2026-10-02  vs  주초 2026-09-28      매수 9종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -656,7 +656,7 @@
         <v>61</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1127304744</v>
+        <v>1119276548</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>-169</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-5930735710</v>
+        <v>-5888499473</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1567885478</v>
+        <v>1556719649</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>-51</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1476417301</v>
+        <v>-1465902870</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>552052968</v>
+        <v>548121476</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>-28</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1409229230</v>
+        <v>-1399193285</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2116203046</v>
+        <v>2101132326</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>-8</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-324390099</v>
+        <v>-322079927</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>791315242</v>
+        <v>785679823</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1008558308</v>
+        <v>1001375774</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>272192783</v>
+        <v>270254339</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>237394572</v>
+        <v>235703947</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>925986283</v>
+        <v>919391793</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,250억   ·   현금 44억(1.3%)      주말 2026-10-02  vs  주초 2026-09-28      매수 7종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,475억   ·   현금 22억(0.6%)      주말 2026-10-02  vs  주초 2026-09-28      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1061,7 +1061,7 @@
         <v>130</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2957564434</v>
+        <v>2957565000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-385</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1558487402</v>
+        <v>-1558487700</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>119</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1801760805</v>
+        <v>1801761150</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-243</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-2096968099</v>
+        <v>-2096968500</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>86</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2410820339</v>
+        <v>2410820800</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-70</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-917080325</v>
+        <v>-917080500</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>50</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>703434866</v>
+        <v>703435000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>-20</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-999975809</v>
+        <v>-999976000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1090716291</v>
+        <v>1090716500</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>-19</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-329908337</v>
+        <v>-329908400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>960227816</v>
+        <v>960228000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>10</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>676238871</v>
+        <v>676239000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,723억   ·   현금 87억(3.0%)      주말 2026-10-02  vs  주초 2026-09-28      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,868억   ·   현금 43억(1.5%)      주말 2026-10-02  vs  주초 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1354,7 +1354,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,988억   ·   현금 20억(0.9%)      주말 2026-10-02  vs  주초 2026-09-28      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,140억   ·   현금 10억(0.5%)      주말 2026-10-02  vs  주초 2026-09-28      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1450,7 +1450,7 @@
         <v>456</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>7160795207</v>
+        <v>7160794413</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>-205</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-2889894930</v>
+        <v>-2889894610</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>279</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2940994474</v>
+        <v>2940994148</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>-60</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2070695771</v>
+        <v>-2070695541</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>221</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>2309659694</v>
+        <v>2309659438</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>-45</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-870731904</v>
+        <v>-870731807</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>31</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>2054667372</v>
+        <v>2054667145</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>-27</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-4849131963</v>
+        <v>-4849131425</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>-12</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-657164327</v>
+        <v>-657164254</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 308억   ·   현금 3억(1.0%)      주말 2026-10-02  vs  주초 2026-09-28      매수 6종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 326억   ·   현금 2억(0.5%)      주말 2026-10-02  vs  주초 2026-09-28      매수 6종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -1743,11 +1743,11 @@
         <v>111</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>78010800</v>
+        <v>80885700</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>6.94%→7.20%</t>
+          <t>6.81%→7.07%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1764,11 +1764,11 @@
         <v>-68</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-182784000</v>
+        <v>-191590000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>7.99%→7.40%</t>
+          <t>7.93%→7.35%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -1787,11 +1787,11 @@
         <v>44</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>62062000</v>
+        <v>67298000</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>2.03%→2.24%</t>
+          <t>2.09%→2.30%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1808,11 +1808,11 @@
         <v>-33</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-45853500</v>
+        <v>-48741000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>3.82%→3.68%</t>
+          <t>3.85%→3.70%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -1831,11 +1831,11 @@
         <v>35</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>62842500</v>
+        <v>63822500</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>4.87%→5.08%</t>
+          <t>4.68%→4.88%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1852,11 +1852,11 @@
         <v>-14</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-39543000</v>
+        <v>-41160000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>2.29%→2.16%</t>
+          <t>2.26%→2.13%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -1868,23 +1868,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>57680000</v>
+        <v>81200000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.23%→2.43%</t>
+          <t>3.74%→4.00%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>238→258</t>
+          <t>299→319</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -1896,11 +1896,11 @@
         <v>-9</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-7623000</v>
+        <v>-7654500</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2.17%→2.15%</t>
+          <t>2.06%→2.04%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -1912,23 +1912,23 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>75320000</v>
+        <v>58380000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>3.67%→3.92%</t>
+          <t>2.14%→2.32%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>238→258</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -1940,11 +1940,11 @@
         <v>-7</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-30870000</v>
+        <v>-34692000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>2.87%→2.77%</t>
+          <t>3.06%→2.95%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -1963,11 +1963,11 @@
         <v>15</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>40057500</v>
+        <v>40215000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>1.10%→1.24%</t>
+          <t>1.05%→1.17%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -1984,11 +1984,11 @@
         <v>-6</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-70434000</v>
+        <v>-77238000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2.98%→2.75%</t>
+          <t>3.09%→2.86%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2012,11 +2012,11 @@
         <v>-5</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-32375000</v>
+        <v>-32795000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.37%→1.27%</t>
+          <t>1.31%→1.21%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2028,7 +2028,7 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 474억   ·   현금 150억(23.0%)      주말 2026-10-02  vs  주초 2026-09-28      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 509억   ·   현금 7억(1.5%)      주말 2026-10-02  vs  주초 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
@@ -2052,7 +2052,7 @@
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,133억      주말 2026-10-02  vs  주초 2026-09-28      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,210억      주말 2026-10-02  vs  주초 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B53" s="4" t="n"/>

--- a/reports/pdf_weekly_20261002.xlsx
+++ b/reports/pdf_weekly_20261002.xlsx
@@ -1868,23 +1868,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>81200000</v>
+        <v>58380000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>3.74%→4.00%</t>
+          <t>2.14%→2.32%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>238→258</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -1912,23 +1912,23 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>58380000</v>
+        <v>81200000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.14%→2.32%</t>
+          <t>3.74%→4.00%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>238→258</t>
+          <t>299→319</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">

--- a/reports/pdf_weekly_20261002.xlsx
+++ b/reports/pdf_weekly_20261002.xlsx
@@ -1274,23 +1274,23 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>960228000</v>
+        <v>676239000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>8.24%→8.23%</t>
+          <t>3.57%→3.68%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G24" s="17" t="n"/>
@@ -1302,23 +1302,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>676239000</v>
+        <v>960228000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>3.57%→3.68%</t>
+          <t>8.24%→8.23%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>

--- a/reports/pdf_weekly_20261002.xlsx
+++ b/reports/pdf_weekly_20261002.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +62,13 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +100,11 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -122,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -162,6 +172,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -553,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-09-28 ~ 2026-10-02  (5거래일)  ·  캡처 7/7</t>
+          <t>주간 변화  ·  2026-09-28 ~ 2026-10-02  (5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -2050,37 +2064,29 @@
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,210억      주말 2026-10-02  vs  주초 2026-09-28      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="20" t="n"/>
+      <c r="E53" s="20" t="n"/>
+      <c r="F53" s="20" t="n"/>
+      <c r="G53" s="20" t="n"/>
+      <c r="H53" s="20" t="n"/>
+      <c r="I53" s="20" t="n"/>
+      <c r="J53" s="20" t="n"/>
+      <c r="K53" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="A51:K51"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G17:K17"/>
-    <mergeCell ref="A54:K54"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A27:K27"/>
     <mergeCell ref="A50:K50"/>

--- a/reports/pdf_weekly_20261002.xlsx
+++ b/reports/pdf_weekly_20261002.xlsx
@@ -1288,23 +1288,23 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>676239000</v>
+        <v>960228000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>3.57%→3.68%</t>
+          <t>8.24%→8.23%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G24" s="17" t="n"/>
@@ -1316,23 +1316,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>960228000</v>
+        <v>676239000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>8.24%→8.23%</t>
+          <t>3.57%→3.68%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
